--- a/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3749" uniqueCount="676">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -692,7 +692,24 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -1366,7 +1383,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2426,20 +2443,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP96"/>
+  <dimension ref="A1:AP97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="26.921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.3203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2448,28 +2465,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.53125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.03515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4874,7 +4891,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>212</v>
       </c>
@@ -4970,7 +4987,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>122</v>
@@ -5030,7 +5047,7 @@
         <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5116,46 +5133,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5203,7 +5218,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5227,7 +5242,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5245,7 +5260,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5258,23 +5273,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5323,7 +5340,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5335,22 +5352,22 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5358,14 +5375,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5384,17 +5401,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5443,7 +5460,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5458,19 +5475,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5478,14 +5495,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5504,18 +5521,18 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5563,7 +5580,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5578,16 +5595,16 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5598,46 +5615,44 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5661,11 +5676,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5683,13 +5700,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5698,30 +5715,30 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5732,31 +5749,31 @@
         <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5781,35 +5798,35 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5818,19 +5835,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5838,14 +5855,12 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5854,7 +5869,7 @@
         <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>94</v>
@@ -5866,19 +5881,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5906,28 +5921,26 @@
         <v>177</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5951,35 +5964,37 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5988,16 +6003,20 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6021,13 +6040,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -6045,19 +6064,19 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6069,10 +6088,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -6080,21 +6099,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -6106,17 +6125,15 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6153,31 +6170,31 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6200,46 +6217,44 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6275,19 +6290,19 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6299,7 +6314,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6308,10 +6323,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6320,12 +6335,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6333,31 +6348,35 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6405,19 +6424,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6426,10 +6445,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6440,21 +6459,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6466,17 +6485,15 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6513,31 +6530,31 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6560,132 +6577,130 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>115</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>116</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6693,13 +6708,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6708,24 +6723,26 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6767,7 +6784,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6805,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6802,10 +6819,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6813,13 +6830,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6828,24 +6845,24 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6887,7 +6904,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6908,10 +6925,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6920,12 +6937,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6933,13 +6950,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6948,27 +6965,27 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>82</v>
@@ -7007,7 +7024,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7028,10 +7045,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7042,10 +7059,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7068,19 +7085,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>332</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7090,7 +7105,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -7129,7 +7144,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7150,10 +7165,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7164,10 +7179,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7190,19 +7205,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>337</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7251,7 +7266,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7272,10 +7287,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7286,24 +7301,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -7312,19 +7327,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7349,13 +7364,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7373,10 +7388,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7388,62 +7403,66 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>108</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7467,13 +7486,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7491,10 +7510,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7503,44 +7522,44 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>111</v>
+        <v>365</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7552,17 +7571,15 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7599,31 +7616,31 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7646,18 +7663,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>81</v>
@@ -7669,23 +7686,21 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7721,9 +7736,11 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7731,7 +7748,7 @@
         <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7743,7 +7760,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7752,10 +7769,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7766,14 +7783,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7782,7 +7797,7 @@
         <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7797,16 +7812,16 @@
         <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7843,19 +7858,17 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7876,10 +7889,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7890,18 +7903,20 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="C46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
@@ -7913,19 +7928,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7973,19 +7992,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7994,10 +8013,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8008,21 +8027,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8034,17 +8053,15 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8081,31 +8098,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8128,21 +8145,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8151,29 +8168,27 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>297</v>
+        <v>115</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>298</v>
+        <v>116</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8203,31 +8218,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>302</v>
+        <v>121</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8236,10 +8251,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>304</v>
+        <v>111</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8250,10 +8265,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8261,7 +8276,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8276,24 +8291,26 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8335,7 +8352,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8356,10 +8373,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8370,10 +8387,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8381,7 +8398,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8396,24 +8413,24 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8455,7 +8472,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8476,10 +8493,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8490,10 +8507,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8501,7 +8518,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8516,24 +8533,24 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8575,7 +8592,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8596,10 +8613,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8610,10 +8627,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8636,19 +8653,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>332</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8697,7 +8712,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8718,10 +8733,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8732,10 +8747,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8758,19 +8773,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>337</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8819,7 +8834,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8840,10 +8855,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8854,10 +8869,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8865,13 +8880,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8880,19 +8895,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>387</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>390</v>
+        <v>349</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8941,7 +8956,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>386</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8956,30 +8971,30 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8987,13 +9002,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9002,18 +9017,20 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9061,13 +9078,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9076,19 +9093,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9096,21 +9113,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9122,20 +9139,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9183,13 +9198,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9198,19 +9213,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9218,24 +9233,24 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9244,19 +9259,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9305,7 +9320,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9314,50 +9329,50 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>421</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9366,18 +9381,20 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>420</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9425,7 +9442,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9434,25 +9451,25 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9460,10 +9477,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9474,7 +9491,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9486,18 +9503,18 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9545,13 +9562,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9560,19 +9577,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9580,10 +9597,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9594,10 +9611,10 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9606,19 +9623,17 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9655,59 +9670,59 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9728,19 +9743,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9777,19 +9792,17 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9798,7 +9811,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9807,29 +9820,31 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9841,25 +9856,29 @@
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>108</v>
+        <v>449</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9907,7 +9926,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>110</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9916,47 +9935,47 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>457</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9968,17 +9987,15 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10015,31 +10032,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10062,46 +10079,44 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>462</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>463</v>
+        <v>115</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>464</v>
+        <v>116</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10137,31 +10152,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>467</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10170,10 +10185,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10182,12 +10197,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10195,83 +10210,83 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>467</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="R65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10292,10 +10307,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10306,10 +10321,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10317,37 +10332,39 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="R66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10367,13 +10384,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10391,7 +10408,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10412,24 +10429,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10452,24 +10469,24 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10511,7 +10528,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10520,7 +10537,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10532,10 +10549,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10544,12 +10561,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10572,26 +10589,24 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -10633,7 +10648,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10642,7 +10657,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10654,10 +10669,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10666,12 +10681,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10679,7 +10694,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>93</v>
@@ -10691,29 +10706,29 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>266</v>
+        <v>173</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10731,13 +10746,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10755,7 +10770,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10764,7 +10779,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10776,10 +10791,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>196</v>
+        <v>492</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10788,26 +10803,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -10816,19 +10831,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10856,10 +10871,10 @@
         <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10877,16 +10892,16 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10895,31 +10910,31 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>524</v>
+        <v>196</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10938,19 +10953,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>528</v>
+        <v>271</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10975,13 +10990,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10999,7 +11014,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11017,27 +11032,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11048,7 +11063,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11060,18 +11075,20 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>266</v>
+        <v>533</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11095,13 +11112,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11119,13 +11136,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11137,27 +11154,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11180,20 +11197,18 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11219,9 +11234,11 @@
       <c r="X73" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Y73" s="2"/>
+      <c r="Y73" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11239,7 +11256,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11257,27 +11274,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11300,18 +11317,20 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11335,13 +11354,11 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11359,7 +11376,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11377,27 +11394,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11411,7 +11428,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11420,16 +11437,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11479,7 +11496,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11497,27 +11514,27 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11528,10 +11545,10 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11540,20 +11557,18 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11601,45 +11616,45 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>577</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11650,7 +11665,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11662,16 +11677,20 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>577</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>108</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11719,19 +11738,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>110</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11740,10 +11759,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>111</v>
+        <v>584</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11754,21 +11773,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11780,17 +11799,15 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11839,19 +11856,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11874,14 +11891,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>583</v>
+        <v>113</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11894,26 +11911,24 @@
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>584</v>
+        <v>115</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>585</v>
+        <v>116</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11961,7 +11976,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>586</v>
+        <v>121</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11985,7 +12000,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12003,26 +12018,26 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>588</v>
+        <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>589</v>
@@ -12030,8 +12045,12 @@
       <c r="M80" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12079,19 +12098,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12100,10 +12119,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>593</v>
+        <v>196</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12114,10 +12133,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12140,13 +12159,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12197,7 +12216,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12206,7 +12225,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12218,10 +12237,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12232,10 +12251,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12258,20 +12277,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>266</v>
+        <v>593</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N82" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>602</v>
-      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12295,13 +12310,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12319,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12328,7 +12343,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12337,13 +12352,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>525</v>
+        <v>602</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12354,10 +12369,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12368,7 +12383,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12380,19 +12395,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12417,13 +12432,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12441,13 +12456,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12459,13 +12474,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12476,10 +12491,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12490,7 +12505,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12502,17 +12517,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12537,13 +12554,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12561,13 +12578,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12579,13 +12596,13 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>619</v>
+        <v>530</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12596,10 +12613,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12622,7 +12639,7 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>620</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>621</v>
@@ -12631,7 +12648,9 @@
         <v>622</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12679,7 +12698,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12700,10 +12719,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12714,10 +12733,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12728,7 +12747,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12737,10 +12756,10 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>625</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>626</v>
@@ -12748,9 +12767,7 @@
       <c r="M86" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>628</v>
-      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12799,13 +12816,13 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
@@ -12820,10 +12837,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12834,10 +12851,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12860,16 +12877,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12919,7 +12936,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12940,10 +12957,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12954,10 +12971,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12971,7 +12988,7 @@
         <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12980,20 +12997,18 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>572</v>
+        <v>637</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>638</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O88" t="s" s="2">
         <v>640</v>
       </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13041,7 +13056,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13053,33 +13068,33 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AN88" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>644</v>
-      </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13090,28 +13105,32 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>577</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>108</v>
+        <v>643</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13159,19 +13178,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>110</v>
+        <v>642</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13180,10 +13199,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>111</v>
+        <v>648</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13194,21 +13213,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13220,17 +13239,15 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13279,19 +13296,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13314,14 +13331,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>583</v>
+        <v>113</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13334,26 +13351,24 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>115</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>116</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O91" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13401,7 +13416,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>121</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13425,7 +13440,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13436,45 +13451,45 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>266</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>648</v>
+        <v>589</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>649</v>
+        <v>590</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>650</v>
+        <v>117</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>651</v>
+        <v>229</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13499,13 +13514,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13523,45 +13538,45 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>647</v>
+        <v>591</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="B93" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13569,7 +13584,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>93</v>
@@ -13584,19 +13599,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13621,13 +13636,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>658</v>
+        <v>360</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>659</v>
+        <v>361</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13645,16 +13660,16 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13663,27 +13678,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>451</v>
+        <v>364</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13703,22 +13718,22 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>266</v>
+        <v>659</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>510</v>
+        <v>451</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13746,10 +13761,10 @@
         <v>155</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>511</v>
+        <v>663</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>512</v>
+        <v>664</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13767,7 +13782,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13776,7 +13791,7 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13785,22 +13800,22 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>666</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>196</v>
+        <v>456</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>514</v>
+        <v>457</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>667</v>
       </c>
@@ -13809,17 +13824,17 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13828,19 +13843,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>517</v>
+        <v>668</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>518</v>
+        <v>669</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>519</v>
+        <v>670</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13868,10 +13883,10 @@
         <v>155</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13895,10 +13910,10 @@
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>82</v>
+        <v>671</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13907,31 +13922,31 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>524</v>
+        <v>196</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13950,19 +13965,19 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>669</v>
+        <v>522</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>670</v>
+        <v>523</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>575</v>
+        <v>524</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>576</v>
+        <v>525</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13987,13 +14002,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14011,7 +14026,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14029,33 +14044,155 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>578</v>
+        <v>529</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP96">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP97">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI96">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
